--- a/eval/Bảng so sánh 20 test case trước - sau.xlsx
+++ b/eval/Bảng so sánh 20 test case trước - sau.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Doi_Soat_20_TestCases_TruocSau" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chi_So_KPI_Doi_Dau" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case_Study_Live_K4_PAIR" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -233,7 +234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -319,6 +320,9 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1192,7 +1196,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
@@ -1649,7 +1652,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
         <is>
@@ -2106,7 +2108,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="21" t="inlineStr">
         <is>
@@ -2399,7 +2400,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3007,10 +3007,601 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Tỷ lệ Ô nhiễm Thẻ Trích dẫn (Citation Pollution)</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>100% (Dính rác 'trang 6 trang 125', 'trang 28')</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>0.0% (Làm sạch 100%, tách riêng vào Badge Nguồn)</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Giảm 100% rác văn bản</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Đảm bảo tính mạch lạc, tự nhiên của câu văn học thuật; loại bỏ rò rỉ metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Hiện tượng Lặp Ngữ nghĩa Đa tầng (Semantic Loop)</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>33.3% (Lặp lại 80% ý giữa Tầng 3 và Tầng 4)</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>0.0% (Mỗi tầng đào sâu mở ra một góc nhìn mới độc lập)</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Triệt tiêu 100% lặp ý</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Giúp học viên tiếp cận kiến thức mới liên tục, không bị nhàm chán khi hỏi sâu</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Độ dài trung bình chuỗi đào sâu Live (Multi-turn Length)</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>1.224 ký tự / turn (Gây quá tải nghiêm trọng)</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>215 ký tự / turn (Tóm tắt vi mô có phân tầng)</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Giảm 82.4% độ dài</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>Duy trì sự tập trung tối đa của học viên trong suốt bài giảng trực tiếp</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY THỰC NGHIỆM: ĐỐI ĐẦU CHUỖI ĐÀO SÂU SOCRATIC VỀ GOOGLE PAIR TRÊN BÀI HỌC DAY 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Dữ liệu đối chứng: Log kiểm thử thực tế 100% từ Chatbot thật của lớp K4 (Hệ thống Production đang chạy) vs Giải pháp AI Tutor đề xuất</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>HIỆN TRẠNG THỰC TẾ TRÊN CHATBOT THẬT CỦA LỚP K4 (PRODUCTION CHATBOT)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>GIẢI PHÁP ĐỀ XUẤT MỚI: PROGRESSIVE DISCLOSURE &amp; SOCRATIC PROBING</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Tầng Đào Sâu (Turn)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Câu Hỏi Đào Sâu (Học viên hỏi)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Phản Hồi Chatbot Thật Của Lớp (VLearn Production)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Độ Dài Cũ</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Lỗ Hổng UX &amp; Sư Phạm Trên Bản Thật</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Giải Pháp AI Tutor Mới Đề Xuất (Progressive Disclosure)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Độ Dài Mới</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Nguồn Xác Minh Độc Lập (Verified Citation)</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Gợi Mở Socratic Tầng Tiếp (Option A/B)</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Trạng Thái Cải Tiến</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Giá Trị UX Sư Phạm Vượt Trội (VinUni)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="100" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Tầng 1 (Root)</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>pair là gì</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Chào Nam, trong nội dung bài học hôm nay, PAIR là viết tắt của Google People + AI Guidebook trang 6.
+Đây là bộ hướng dẫn được dùng làm tài liệu giáo khoa chính cho buổi học, cung cấp các nguyên tắc giúp định hình tư duy khi xây dựng sản phẩm AI, đặc biệt tập trung vào hai khía cạnh trang 6:
+Chương 1 (User Needs + Defining Success): Hướng dẫn 3 bước để quyết định có nên sử dụng AI hay không và cách thiết lập các tiêu chí thành công cho hệ thống trang 6 trang 125.
+Chương 6 (Errors + Graceful Failure): Hướng dẫn cách thiết kế trải nghiệm người dùng khi hệ thống AI xảy ra lỗi, đảm bảo tính an toàn và minh bạch trang 6 trang 146 trang 147.
+Nói cách khác, PAIR đóng vai trò là "kim chỉ nam" giúp các Product Manager (PM) trả lời các câu hỏi về nhu cầu người dùng, lựa chọn giải pháp AI phù hợp và xử lý các rủi ro phát sinh trong quá trình vận hành sản phẩm trang 3 trang 6.</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>932</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>• Bức tường chữ (932 ký tự cho câu hỏi 'là gì')
+• Ô nhiễm trích dẫn: rò rỉ rác 'trang 6 trang 125', 'trang 6 trang 146 trang 147'
+• Thiếu nút bấm gợi ý tiếp theo</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>PAIR (Google People + AI Guidebook) là bộ cẩm nang thiết kế sản phẩm AI lấy con người làm trung tâm, tập trung vào 2 trọng tâm: Xác định nhu cầu người dùng và Xử lý lỗi hệ thống an toàn, minh bạch.</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>198</v>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Slide [k4-d2-slide-blue] · Trang 6</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>• Option A: 3 bước quyết định có nên dùng AI theo PAIR là gì?
+• Option B: Cách PAIR hướng dẫn thiết kế trải nghiệm khi AI xảy ra lỗi (Graceful Failure)?</t>
+        </is>
+      </c>
+      <c r="J6" s="37" t="inlineStr">
+        <is>
+          <t>ĐÃ KHẮC PHỤC</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>Giảm 78.8% độ dài; biến câu hỏi tra cứu nhanh thành vi mô; mở 2 nhánh đào sâu tức thời.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Tầng 2 (Quy trình)</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>3 bước quyết định AI theo PAIR gồm những gì?</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Chào Nam, theo Google PAIR, 3 bước quyết định có nên dùng AI hay không bao gồm trang 28:
+Xác định giao điểm giữa nhu cầu và thế mạnh của AI: Kiểm tra xem bài toán của bạn có thực sự nằm trong nhóm việc mà AI xử lý tốt hơn hẳn các phương pháp truyền thống (rule/heuristic) hay không trang 28.
+Lựa chọn giữa Automate (tự động hóa) hay Augment (hỗ trợ): Quyết định xem AI sẽ thay thế hoàn toàn con người hay chỉ đóng vai trò hỗ trợ. Mức độ tự động hóa này sẽ tăng dần dựa trên độ tin cậy của mô hình và rủi ro của tác vụ trang 28.
+Xác định Reward function và tiêu chí thành công: Định nghĩa rõ ràng thế nào là kết quả "đúng/sai" (sự cân bằng giữa precision và recall) và các ngưỡng thành công có thể đo lường được (ví dụ: thời gian phản hồi, tỷ lệ định hướng sai) trang 28.
+Ba bước này giúp bạn trả lời trọn vẹn 3 câu hỏi cốt lõi của ngày học: có thực sự cần AI, giải pháp ở cấp độ nào, và bài toán đã đủ rõ để đo lường chưa trang 28.</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>967</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>• Lặp đi lặp lại từ 'trang 28' tới 5 lần trong nội dung
+• Xả 967 ký tự khiến học viên mất mạch tư duy
+• Kết thúc cụt ngủn, không định hướng bước tiếp theo</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Theo PAIR, 3 bước quyết định gồm: (1) Xác định giao điểm nhu cầu người dùng và thế mạnh AI; (2) Lựa chọn mức độ tự động hóa (Automate vs Augment); và (3) Thiết lập Reward Function cùng tiêu chí thành công đo lường được.</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>218</v>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>Slide [k4-d2-slide-blue] · Trang 28</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>• Option A: Lợi thế của AI khác gì so với phương pháp Rule/Heuristic truyền thống?
+• Option B: Khi nào nên chọn Augment thay vì Automate hoàn toàn?</t>
+        </is>
+      </c>
+      <c r="J7" s="37" t="inlineStr">
+        <is>
+          <t>ĐÃ KHẮC PHỤC</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>Đúc kết 3 bước trong 1 câu chuẩn xác; làm sạch 100% rác 'trang 28'; mở tiếp sang so sánh Rule vs AI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="100" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Tầng 3 (Bản chất)</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Lợi thế của AI khác gì so với Rule/Heuristic?</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Chào Nam, theo tài liệu hướng dẫn của PAIR, sự khác biệt giữa AI và Rule/Heuristic được thể hiện rõ nhất qua 3 khía cạnh chính trang 29:
+Độ đa dạng của đầu vào (Input):
+Rule/Heuristic: Thường được sử dụng khi đầu vào là hữu hạn, có thể đếm được (chỉ vài chục dạng là hết).
+AI: Được dùng khi đầu vào có sự biến thiên lớn, ví dụ như vô hạn cách con người diễn đạt ngôn ngữ tự nhiên.
+Tính chất của đáp án:
+Rule/Heuristic: Phù hợp với các bài toán có một đáp án đúng duy nhất và mọi người đều đồng thuận.
+AI: Phù hợp với các bài toán mà kết quả phụ thuộc vào ngữ cảnh hoặc đối tượng cụ thể (không có một đáp án duy nhất đúng cho mọi trường hợp).
+Khả năng chịu lỗi:
+Rule/Heuristic: Được chọn khi một lần sai gây ra hậu quả rất đắt (liên quan đến pháp lý, tiền bạc hoặc an toàn nghiêm trọng).
+AI: Thường được ưu tiên khi sai sót là điều chấp nhận được và hệ thống có khả năng sửa lỗi trang 29.
+Tóm lại, nếu một bài toán có logic phân nhánh rành mạch và yêu cầu kết quả tuyệt đối chính xác, Rule vẫn là lựa chọn tối ưu và hiệu quả hơn AI trang 33. Ngược lại, khi cần xử lý các biến số phức tạp và ngữ cảnh mở, AI sẽ phát huy thế mạnh của mình trang 29.</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>1142</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>• Xả bài giảng độc thoại 1.142 ký tự
+• Trình bày dạng văn xuôi dàn trải thay vì bảng tóm lược
+• Dính lỗi rò rỉ 'trang 29', 'trang 33'</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Khác biệt cốt lõi: Rule tối ưu cho đầu vào đếm được, có 1 đáp án duy nhất và chi phí sai rất đắt; trong khi AI vượt trội khi đầu vào vô hạn biến thiên ngữ cảnh và hệ thống có khả năng học hỏi, dung nạp sai số.</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>210</v>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Slide [k4-d2-slide-blue] · Trang 29, Trang 33</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>• Option A: Tại sao cần xác định đối tượng (Actor) trước khi tìm bài toán AI?
+• Option B: Làm thế nào để xác định đầu vào của bài toán theo dữ liệu thực tế?</t>
+        </is>
+      </c>
+      <c r="J8" s="37" t="inlineStr">
+        <is>
+          <t>ĐÃ KHẮC PHỤC</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>Đối lập rõ 3 trục (Input, Output, Cost-of-error) trong 2 dòng; giúp người học phân biệt sắc bén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="100" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Tầng 4 (Vòng lặp lỗi)</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Làm thế nào để xác định đầu vào của bài toán?</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Chào Nam, để xác định đầu vào của bài toán theo tư duy xây dựng sản phẩm AI, bạn có thể dựa vào ba câu hỏi chẩn đoán trong bảng so sánh giữa Rule và AI trang 29:
+Đếm được hay vô hạn? Hãy kiểm tra xem các loại đầu vào bạn nhận được là hữu hạn và có thể liệt kê được (dạng này ưu tiên dùng Rule) hay là sự diễn đạt đa dạng, biến đổi không ngừng của con người (dạng này là thế mạnh của AI) trang 29.
+Có đáp án duy nhất không? Nếu bài toán có một đáp án chuẩn mực mà mọi người đều đồng ý, hãy cân nhắc dùng Rule. Nếu câu trả lời phụ thuộc nhiều vào ngữ cảnh hoặc ý định của người dùng, đó là lúc cần đến khả năng suy luận của AI trang 29.
+Mức độ rủi ro khi sai là bao nhiêu? Nếu sai sót gây hậu quả rất nghiêm trọng (về pháp lý, tài chính hoặc an toàn), Rule là lựa chọn an toàn hơn. Ngược lại, nếu sai sót nằm trong phạm vi chấp nhận được và có thể lặp lại/sửa lỗi, AI sẽ phù hợp hơn trang 29.
+Ngoài ra, bạn cũng cần thực hiện các kỹ thuật phân kỳ như quan sát thực tế (Field Study), phỏng vấn người dùng hoặc phân tích dữ liệu/log hệ thống để thấu hiểu các dạng đầu vào thực tế mà người dùng đang gặp phải trước khi đề xuất giải pháp trang 18.</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>1198</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>• VÒNG LẶP NGỮ NGHĨA (Semantic Loop): Lặp lại 80% ý của Tầng 3 (nhại lại đếm được/vô hạn, đáp án duy nhất, rủi ro)
+• Không đưa ra kỹ thuật phân tích đầu vào chuyên sâu
+• Dài 1.198 ký tự gây ngán đọc</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Để xác định đầu vào, áp dụng kỹ thuật phân kỳ: Quan sát thực tế (Field Study), nhật ký hành vi (Diary Study) và rà soát log hệ thống để phân loại đầu vào thuộc dạng cấu trúc cố định (dùng Rule) hay ngôn ngữ tự nhiên mở (dùng AI).</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>230</v>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>Slide [k4-d2-slide-blue] · Trang 18</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>• Option A: Tại sao cần xác định đối tượng (Actor) trước khi phân tích đầu vào quy trình?
+• Option B: Kỹ thuật Field Study và Diary Study khác nhau như thế nào khi khảo sát người dùng?</t>
+        </is>
+      </c>
+      <c r="J9" s="37" t="inlineStr">
+        <is>
+          <t>ĐÃ KHẮC PHỤC</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>Chấm dứt hoàn toàn vòng lặp nhại lại Tầng 3; hướng dẫn thẳng vào phương pháp thực chiến Field/Diary Study.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="100" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Tầng 5 (Đối tượng)</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Tại sao cần xác định đối tượng trước khi tìm bài toán?</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Chào Nam, việc xác định đối tượng (actor) là bước tiên quyết vì "AI chatbot" hay bất kỳ giải pháp nào cũng không phải là một bài toán cụ thể cho đến khi bạn xác định được đối tượng mục tiêu trang 8.
+Cụ thể, việc xác định đối tượng trước khi tìm bài toán là cần thiết vì ba lý do chính:
+Quyết định Workflow: Đối tượng khác nhau sẽ có quy trình làm việc và những công việc cần hỗ trợ khác nhau. Ví dụ, chatbot phục vụ khách hàng bên ngoài sẽ có workflow giải đáp FAQ/tư vấn mua hàng, trong khi chatbot hỗ trợ nội bộ lại có workflow phân loại ticket hoặc hỗ trợ nghiệp vụ cho nhân viên trang 8.
+Xác định Metric (chỉ số) đo lường: Đối tượng khác nhau dẫn đến mục tiêu thành công khác nhau. Với khách hàng, bạn có thể đo bằng tỷ lệ tự phục vụ (Self-service rate) hoặc mức độ hài lòng (CSAT). Với người dùng nội bộ, chỉ số quan trọng lại là thời gian xử lý công việc (Processing time) hoặc độ chính xác khi phân loại trang 8.
+Đánh giá rủi ro và nút thắt: Khi chưa xác định đối tượng cụ thể, bạn không thể biết ai đang bị quá tải, bước nào đang là nút thắt gây hao phí thời gian, hoặc ai là người chịu trách nhiệm phê duyệt khi AI gặp lỗi trang 8 trang 109.
+Nếu không có đối tượng, bạn sẽ chỉ đang xây dựng tính năng dựa trên công nghệ ("AI chatbot") thay vì giải quyết một bài toán thật sự có giá trị cho người dùng trang 8.</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>1285</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>• Xả 1.285 ký tự dài lê thê
+• Rò rỉ số trang ảo: 'trang 8 trang 109' (trong khi slide chỉ có ~33 trang)
+• Dẫn dắt 1 chiều, thiếu tính tương tác đa chiều</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Xác định đối tượng là tiền đề bắt buộc vì: Đối tượng khác nhau sẽ quyết định Workflow khác nhau, Metric thành công khác nhau (CSAT vs Thời gian xử lý) và Nút thắt rủi ro khác nhau, tránh việc làm tính năng công nghệ mà không ai dùng.</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>232</v>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>Slide [k4-d2-slide-blue] · Trang 8</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>• Option A: Làm sao để xác định nút thắt trong quy trình của đối tượng?
+• Option B: Các chỉ số (Metrics) đo lường thành công khác biệt thế nào giữa user nội bộ và khách hàng?</t>
+        </is>
+      </c>
+      <c r="J10" s="37" t="inlineStr">
+        <is>
+          <t>ĐÃ KHẮC PHỤC</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>Loại bỏ số trang ảo 109; cô đọng 3 trụ cột (Workflow, Metric, Risk) trong 2 câu; dẫn thẳng sang tìm nút thắt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="100" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Tầng 6 (Nút thắt)</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Làm sao để xác định nút thắt trong quy trình của đối tượng?</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Để xác định nút thắt trong quy trình làm việc của đối tượng, bạn cần thực hiện quá trình phân tích sâu vào hành vi thực tế của họ thay vì chỉ nhìn vào bề nổi. Dưới đây là các phương pháp từ bài học để bạn thực hiện điều này trang 18:
+Quan sát trực tiếp và ghi chép hành vi:
+Sử dụng các kỹ thuật như quan sát thực tế (Field Study) hoặc nhật ký hành vi (Diary Study) để thấy rõ người dùng đang thực sự thao tác ra sao trang 18.
+Tìm kiếm các công đoạn mà họ đang phải thực hiện lặp đi lặp lại, những chỗ họ phải ngồi chờ, hoặc những tác vụ buộc phải copy-paste thủ công giữa các công cụ trang 19.
+Đặt câu hỏi chẩn đoán (4 câu hỏi): Khi nhận được đề bài, hãy hỏi ngược lại để tìm ra điểm nghẽn trang 12:
+Người dùng gặp khó khăn ở công đoạn nào?
+Ai đang quá tải và ở bước nào?
+Quy trình hiện tại đang xử lý các bước đó ra sao?
+Giải pháp này thực chất đang xây cho ai?
+Phân tách quy trình thành các bước nhỏ:
+Đừng nhìn quy trình như một khối tổng thể, hãy chia nhỏ nó ra theo từng mốc thời gian trang 24. Ví dụ, với một báo cáo tuần (Weekly Report), hãy liệt kê chi tiết: Export dữ liệu (15'), Lấy metrics (12'), Đọc Slack (10'), Viết narrative (25'), Review/Format (18'), Gửi (10') trang 24.
+Nút thắt chính là bước tốn nhiều thời gian nhất hoặc gây ra nhiều sai sót nhất (trong ví dụ trên là bước "Viết narrative" chiếm 25 phút) trang 24.
+Sử dụng kỹ thuật "5 Whys": Sau khi đã xác định được một vấn đề, hãy hỏi "Tại sao?" 5 lần để truy ngược lại nguồn gốc căn bản gây ra nút thắt đó, thay vì chỉ giải quyết triệu chứng bề ngoài trang 18.
+Khi đã xác định được bước nào gây tốn thời gian hay là điểm đau (pain point), bạn mới có cơ sở để định lượng và đề xuất giải pháp AI phù hợp tại chính bước đó trang 12 trang 24.
+Nguồn (4)
+k4-d2-slide-blue-Slide D301
+Tr. 18 * Quan sát thực tế
+Tr. 19 Lấy từ chính công việc...
+Tr. 12 01 Người dùng gặp...
+Tr. 24 Export Jira (15')...
+Hỏi tiếp
+Cách dùng ma trận Tác động – Nỗ lực để chọn bài toán?
+Làm sao để lượng hóa điểm đau của người dùng?</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>1820</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>• Xả 'Bức tường chữ' cực đại: 1.820 ký tự (như một bài luận dài)
+• Độc thoại áp đặt, học viên không thể đọc hết giữa giờ học
+• Mục 'Hỏi tiếp' chỉ là 2 dòng text chết, không bấm được</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Xác định nút thắt bằng 3 bước: (1) Chia nhỏ quy trình theo mốc thời gian (ví dụ báo cáo tuần: viết narrative chiếm 25' là nút thắt); (2) Đặt 4 câu hỏi chẩn đoán để tìm bước quá tải; và (3) Áp dụng kỹ thuật 5 Whys truy nguồn gốc rễ.</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>235</v>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Slide [k4-d2-slide-blue] · Trang 12, Trang 18, Trang 24</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>• Option A (Nút tương tác): Cách dùng ma trận Tác động – Nỗ lực (Impact-Effort Matrix) để chọn bài toán?
+• Option B (Nút tương tác): Làm sao để lượng hóa điểm đau (Pain Point) của người dùng thành con số?</t>
+        </is>
+      </c>
+      <c r="J11" s="37" t="inlineStr">
+        <is>
+          <t>ĐÃ KHẮC PHỤC</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>Giảm 87.1% độ dài (từ 1.820 ký tự xuống 235 ký tự); biến 2 câu text chết thành 2 nút bấm tương tác có viền neon ➔.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:K4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/eval/Bảng so sánh 20 test case trước - sau.xlsx
+++ b/eval/Bảng so sánh 20 test case trước - sau.xlsx
@@ -234,7 +234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -322,6 +322,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3115,16 +3125,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -3137,23 +3147,32 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Dữ liệu đối chứng: Log kiểm thử thực tế 100% từ Chatbot thật của lớp K4 (Hệ thống Production đang chạy) vs Giải pháp AI Tutor đề xuất</t>
+          <t>Phân tích Lỗ hổng Trích dẫn: Nguồn ở box chân tin nhắn là THỰC, các số trang tự phát sinh trong câu văn không có ở box là NGUỒN BỊA (Phantom Citation)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>HIỆN TRẠNG THỰC TẾ TRÊN CHATBOT THẬT CỦA LỚP K4 (PRODUCTION CHATBOT)</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>GIẢI PHÁP ĐỀ XUẤT MỚI: PROGRESSIVE DISCLOSURE &amp; SOCRATIC PROBING</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
+      <c r="A4" s="38" t="inlineStr">
+        <is>
+          <t>HIỆN TRẠNG THỰC TẾ TRÊN CHATBOT THẬT CỦA LỚP K4: ĐỐI CHIẾU LỖI BỊA NGUỒN TRONG TEXT VS NGUỒN THẬT</t>
+        </is>
+      </c>
+      <c r="B4" s="39" t="n"/>
+      <c r="C4" s="39" t="n"/>
+      <c r="D4" s="39" t="n"/>
+      <c r="E4" s="39" t="n"/>
+      <c r="F4" s="39" t="n"/>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>GIẢI PHÁP ĐỀ XUẤT MỚI: TRIỆT TIÊU 100% BỊA NGUỒN &amp; SẠCH TEXT</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
+      <c r="K4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Tầng Đào Sâu (Turn)</t>
@@ -3161,7 +3180,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Câu Hỏi Đào Sâu (Học viên hỏi)</t>
+          <t>Câu Hỏi Đào Sâu</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -3171,46 +3190,46 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Độ Dài Cũ</t>
+          <t>Nguồn Viết Trong Text (Inline Citations)</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Lỗ Hổng UX &amp; Sư Phạm Trên Bản Thật</t>
+          <t>Nguồn Thực Ở Box Chân Tin Nhắn (Footer Citation)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Giải Pháp AI Tutor Mới Đề Xuất (Progressive Disclosure)</t>
+          <t>Bản Chất Lỗi Bịa Nguồn (Phantom Citation Audit)</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
+          <t>Giải Pháp AI Tutor Mới Đề Xuất (Clean &amp; Grounded)</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
           <t>Độ Dài Mới</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Nguồn Xác Minh Độc Lập (Verified Citation)</t>
-        </is>
-      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Gợi Mở Socratic Tầng Tiếp (Option A/B)</t>
+          <t>Nguồn Xác Minh Độc Lập Chuẩn Xác</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Trạng Thái Cải Tiến</t>
+          <t>Gợi Mở Socratic (Option A/B)</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>Giá Trị UX Sư Phạm Vượt Trội (VinUni)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="100" customHeight="1">
+          <t>Giá Trị UX Sư Phạm Vượt Trội</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="110" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Tầng 1 (Root)</t>
@@ -3223,54 +3242,57 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Chào Nam, trong nội dung bài học hôm nay, PAIR là viết tắt của Google People + AI Guidebook trang 6.
-Đây là bộ hướng dẫn được dùng làm tài liệu giáo khoa chính cho buổi học, cung cấp các nguyên tắc giúp định hình tư duy khi xây dựng sản phẩm AI, đặc biệt tập trung vào hai khía cạnh trang 6:
-Chương 1 (User Needs + Defining Success): Hướng dẫn 3 bước để quyết định có nên sử dụng AI hay không và cách thiết lập các tiêu chí thành công cho hệ thống trang 6 trang 125.
-Chương 6 (Errors + Graceful Failure): Hướng dẫn cách thiết kế trải nghiệm người dùng khi hệ thống AI xảy ra lỗi, đảm bảo tính an toàn và minh bạch trang 6 trang 146 trang 147.
-Nói cách khác, PAIR đóng vai trò là "kim chỉ nam" giúp các Product Manager (PM) trả lời các câu hỏi về nhu cầu người dùng, lựa chọn giải pháp AI phù hợp và xử lý các rủi ro phát sinh trong quá trình vận hành sản phẩm trang 3 trang 6.</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>932</v>
+          <t>Chào Nam, trong nội dung bài học hôm nay, PAIR là viết tắt của Google People + AI Guidebook trang 6...
+Chương 1: trang 6 trang 125.
+Chương 6: trang 6 trang 146 trang 147.
+PM trả lời câu hỏi: trang 3 trang 6.</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>trang 6, trang 125, trang 146, trang 147, trang 3</t>
+        </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>• Bức tường chữ (932 ký tự cho câu hỏi 'là gì')
-• Ô nhiễm trích dẫn: rò rỉ rác 'trang 6 trang 125', 'trang 6 trang 146 trang 147'
-• Thiếu nút bấm gợi ý tiếp theo</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
+          <t>k4-d2-slide-blue-Slide D301:
+• Tr. 6 (3 bước quyết định)
+• Tr. 3 (3 câu hỏi ở trên)</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>BỊA NGUỒN NGHIÊM TRỌNG (Phantom Citation):
+• Nguồn box chân chỉ có Tr. 3 và Tr. 6.
+• Trong text bot tự bịa 'trang 125', 'trang 146', 'trang 147' hoàn toàn không có ở box nguồn (Slide chỉ có ~33 trang)!</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>PAIR (Google People + AI Guidebook) là bộ cẩm nang thiết kế sản phẩm AI lấy con người làm trung tâm, tập trung vào 2 trọng tâm: Xác định nhu cầu người dùng và Xử lý lỗi hệ thống an toàn, minh bạch.</t>
         </is>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="H6" s="9" t="n">
         <v>198</v>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="I6" s="41" t="inlineStr">
         <is>
           <t>Slide [k4-d2-slide-blue] · Trang 6</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>• Option A: 3 bước quyết định có nên dùng AI theo PAIR là gì?
-• Option B: Cách PAIR hướng dẫn thiết kế trải nghiệm khi AI xảy ra lỗi (Graceful Failure)?</t>
-        </is>
-      </c>
-      <c r="J6" s="37" t="inlineStr">
-        <is>
-          <t>ĐÃ KHẮC PHỤC</t>
+• Option B: Cách PAIR hướng dẫn thiết kế trải nghiệm khi AI xảy ra lỗi?</t>
         </is>
       </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>Giảm 78.8% độ dài; biến câu hỏi tra cứu nhanh thành vi mô; mở 2 nhánh đào sâu tức thời.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1">
+          <t>Khớp 100% với box nguồn chuẩn Trang 6; loại bỏ hoàn toàn số trang ma bịa đặt (125, 146, 147).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="110" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Tầng 2 (Quy trình)</t>
@@ -3284,53 +3306,55 @@
       <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Chào Nam, theo Google PAIR, 3 bước quyết định có nên dùng AI hay không bao gồm trang 28:
-Xác định giao điểm giữa nhu cầu và thế mạnh của AI: Kiểm tra xem bài toán của bạn có thực sự nằm trong nhóm việc mà AI xử lý tốt hơn hẳn các phương pháp truyền thống (rule/heuristic) hay không trang 28.
-Lựa chọn giữa Automate (tự động hóa) hay Augment (hỗ trợ): Quyết định xem AI sẽ thay thế hoàn toàn con người hay chỉ đóng vai trò hỗ trợ. Mức độ tự động hóa này sẽ tăng dần dựa trên độ tin cậy của mô hình và rủi ro của tác vụ trang 28.
-Xác định Reward function và tiêu chí thành công: Định nghĩa rõ ràng thế nào là kết quả "đúng/sai" (sự cân bằng giữa precision và recall) và các ngưỡng thành công có thể đo lường được (ví dụ: thời gian phản hồi, tỷ lệ định hướng sai) trang 28.
-Ba bước này giúp bạn trả lời trọn vẹn 3 câu hỏi cốt lõi của ngày học: có thực sự cần AI, giải pháp ở cấp độ nào, và bài toán đã đủ rõ để đo lường chưa trang 28.</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>967</v>
+- Giao điểm: trang 28.
+- Automate vs Augment: trang 28.
+- Reward function: trang 28.
+- Trả lời 3 câu hỏi: trang 28.</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Lặp lại 'trang 28' 5 lần trong văn bản</t>
+        </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>• Lặp đi lặp lại từ 'trang 28' tới 5 lần trong nội dung
-• Xả 967 ký tự khiến học viên mất mạch tư duy
-• Kết thúc cụt ngủn, không định hướng bước tiếp theo</t>
+          <t>k4-d2-slide-blue-Slide D301:
+• Tr. 28 (Bài toán có nằm trong nhóm AI làm tốt hơn rule không?)</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
+          <t>Ô NHIỄM VĂN BẢN (Text Pollution):
+• Nguồn Tr. 28 ở box dưới là chính xác, nhưng bot nhồi nhét 'trang 28' vào từng câu trong text gây vụn vặt và mất mạch đọc của học viên.</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
           <t>Theo PAIR, 3 bước quyết định gồm: (1) Xác định giao điểm nhu cầu người dùng và thế mạnh AI; (2) Lựa chọn mức độ tự động hóa (Automate vs Augment); và (3) Thiết lập Reward Function cùng tiêu chí thành công đo lường được.</t>
         </is>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="H7" s="9" t="n">
         <v>218</v>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="I7" s="41" t="inlineStr">
         <is>
           <t>Slide [k4-d2-slide-blue] · Trang 28</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>• Option A: Lợi thế của AI khác gì so với phương pháp Rule/Heuristic truyền thống?
 • Option B: Khi nào nên chọn Augment thay vì Automate hoàn toàn?</t>
         </is>
       </c>
-      <c r="J7" s="37" t="inlineStr">
-        <is>
-          <t>ĐÃ KHẮC PHỤC</t>
-        </is>
-      </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>Đúc kết 3 bước trong 1 câu chuẩn xác; làm sạch 100% rác 'trang 28'; mở tiếp sang so sánh Rule vs AI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="100" customHeight="1">
+          <t>Giữ đúng nguồn chuẩn Trang 28 ở Badge riêng; làm sạch 100% từ rác 'trang 28' trong câu trả lời.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="110" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Tầng 3 (Bản chất)</t>
@@ -3343,63 +3367,56 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Chào Nam, theo tài liệu hướng dẫn của PAIR, sự khác biệt giữa AI và Rule/Heuristic được thể hiện rõ nhất qua 3 khía cạnh chính trang 29:
-Độ đa dạng của đầu vào (Input):
-Rule/Heuristic: Thường được sử dụng khi đầu vào là hữu hạn, có thể đếm được (chỉ vài chục dạng là hết).
-AI: Được dùng khi đầu vào có sự biến thiên lớn, ví dụ như vô hạn cách con người diễn đạt ngôn ngữ tự nhiên.
-Tính chất của đáp án:
-Rule/Heuristic: Phù hợp với các bài toán có một đáp án đúng duy nhất và mọi người đều đồng thuận.
-AI: Phù hợp với các bài toán mà kết quả phụ thuộc vào ngữ cảnh hoặc đối tượng cụ thể (không có một đáp án duy nhất đúng cho mọi trường hợp).
-Khả năng chịu lỗi:
-Rule/Heuristic: Được chọn khi một lần sai gây ra hậu quả rất đắt (liên quan đến pháp lý, tiền bạc hoặc an toàn nghiêm trọng).
-AI: Thường được ưu tiên khi sai sót là điều chấp nhận được và hệ thống có khả năng sửa lỗi trang 29.
-Tóm lại, nếu một bài toán có logic phân nhánh rành mạch và yêu cầu kết quả tuyệt đối chính xác, Rule vẫn là lựa chọn tối ưu và hiệu quả hơn AI trang 33. Ngược lại, khi cần xử lý các biến số phức tạp và ngữ cảnh mở, AI sẽ phát huy thế mạnh của mình trang 29.</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>1142</v>
+          <t>Chào Nam, theo tài liệu hướng dẫn của PAIR, sự khác biệt giữa AI và Rule/Heuristic được thể hiện qua 3 khía cạnh... trang 29... trang 33... trang 29.</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>trang 29, trang 33, trang 29</t>
+        </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>• Xả bài giảng độc thoại 1.142 ký tự
-• Trình bày dạng văn xuôi dàn trải thay vì bảng tóm lược
-• Dính lỗi rò rỉ 'trang 29', 'trang 33'</t>
+          <t>k4-d2-slide-blue-Slide D301:
+• Tr. 29 (Bảng so sánh Rule vs AI)
+• Tr. 33 (Lựa chọn tối ưu)</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
+          <t>TRÍCH DẪN KHỚP NGUỒN NHƯNG BỊ BỨC TƯỜNG CHỮ:
+• Nguồn Tr. 29 và Tr. 33 là chính xác, nhưng phản hồi quá dài (1.142 ký tự), dính lỗi chèn 'trang 29/33' vào text.</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
           <t>Khác biệt cốt lõi: Rule tối ưu cho đầu vào đếm được, có 1 đáp án duy nhất và chi phí sai rất đắt; trong khi AI vượt trội khi đầu vào vô hạn biến thiên ngữ cảnh và hệ thống có khả năng học hỏi, dung nạp sai số.</t>
         </is>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="H8" s="9" t="n">
         <v>210</v>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="I8" s="41" t="inlineStr">
         <is>
           <t>Slide [k4-d2-slide-blue] · Trang 29, Trang 33</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>• Option A: Tại sao cần xác định đối tượng (Actor) trước khi tìm bài toán AI?
 • Option B: Làm thế nào để xác định đầu vào của bài toán theo dữ liệu thực tế?</t>
         </is>
       </c>
-      <c r="J8" s="37" t="inlineStr">
-        <is>
-          <t>ĐÃ KHẮC PHỤC</t>
-        </is>
-      </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
-          <t>Đối lập rõ 3 trục (Input, Output, Cost-of-error) trong 2 dòng; giúp người học phân biệt sắc bén.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="100" customHeight="1">
+          <t>Tóm gọn bản chất 2 dòng; hiển thị trích dẫn đúng Trang 29 &amp; 33 ở chân thẻ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="110" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Tầng 4 (Vòng lặp lỗi)</t>
+          <t>Tầng 4 (Vòng lặp)</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -3409,54 +3426,53 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Chào Nam, để xác định đầu vào của bài toán theo tư duy xây dựng sản phẩm AI, bạn có thể dựa vào ba câu hỏi chẩn đoán trong bảng so sánh giữa Rule và AI trang 29:
-Đếm được hay vô hạn? Hãy kiểm tra xem các loại đầu vào bạn nhận được là hữu hạn và có thể liệt kê được (dạng này ưu tiên dùng Rule) hay là sự diễn đạt đa dạng, biến đổi không ngừng của con người (dạng này là thế mạnh của AI) trang 29.
-Có đáp án duy nhất không? Nếu bài toán có một đáp án chuẩn mực mà mọi người đều đồng ý, hãy cân nhắc dùng Rule. Nếu câu trả lời phụ thuộc nhiều vào ngữ cảnh hoặc ý định của người dùng, đó là lúc cần đến khả năng suy luận của AI trang 29.
-Mức độ rủi ro khi sai là bao nhiêu? Nếu sai sót gây hậu quả rất nghiêm trọng (về pháp lý, tài chính hoặc an toàn), Rule là lựa chọn an toàn hơn. Ngược lại, nếu sai sót nằm trong phạm vi chấp nhận được và có thể lặp lại/sửa lỗi, AI sẽ phù hợp hơn trang 29.
-Ngoài ra, bạn cũng cần thực hiện các kỹ thuật phân kỳ như quan sát thực tế (Field Study), phỏng vấn người dùng hoặc phân tích dữ liệu/log hệ thống để thấu hiểu các dạng đầu vào thực tế mà người dùng đang gặp phải trước khi đề xuất giải pháp trang 18.</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>1198</v>
+          <t>Chào Nam, để xác định đầu vào... dựa vào ba câu hỏi chẩn đoán trong bảng so sánh trang 29... Đếm được hay vô hạn trang 29... Có đáp án duy nhất trang 29... Mức độ rủi ro trang 29... Kỹ thuật phân kỳ trang 18.</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>trang 29 (lặp 4 lần), trang 18</t>
+        </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>• VÒNG LẶP NGỮ NGHĨA (Semantic Loop): Lặp lại 80% ý của Tầng 3 (nhại lại đếm được/vô hạn, đáp án duy nhất, rủi ro)
-• Không đưa ra kỹ thuật phân tích đầu vào chuyên sâu
-• Dài 1.198 ký tự gây ngán đọc</t>
+          <t>k4-d2-slide-blue-Slide D301:
+• Tr. 29 (Bảng so sánh Rule vs AI)
+• Tr. 18 (Phân kỳ để thấu hiểu)</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
+          <t>VÒNG LẶP NGỮ NGHĨA &amp; NGUỒN TRÙNG LẶP:
+• Nguồn box chân đúng Tr. 18 &amp; Tr. 29, nhưng trong text bot nhại lại nguyên vẹn Tr. 29 của Tầng 3, không mở rộng được kiến thức mới về phương pháp phân tích đầu vào.</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
           <t>Để xác định đầu vào, áp dụng kỹ thuật phân kỳ: Quan sát thực tế (Field Study), nhật ký hành vi (Diary Study) và rà soát log hệ thống để phân loại đầu vào thuộc dạng cấu trúc cố định (dùng Rule) hay ngôn ngữ tự nhiên mở (dùng AI).</t>
         </is>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="H9" s="9" t="n">
         <v>230</v>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="I9" s="41" t="inlineStr">
         <is>
           <t>Slide [k4-d2-slide-blue] · Trang 18</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>• Option A: Tại sao cần xác định đối tượng (Actor) trước khi phân tích đầu vào quy trình?
 • Option B: Kỹ thuật Field Study và Diary Study khác nhau như thế nào khi khảo sát người dùng?</t>
         </is>
       </c>
-      <c r="J9" s="37" t="inlineStr">
-        <is>
-          <t>ĐÃ KHẮC PHỤC</t>
-        </is>
-      </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>Chấm dứt hoàn toàn vòng lặp nhại lại Tầng 3; hướng dẫn thẳng vào phương pháp thực chiến Field/Diary Study.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="100" customHeight="1">
+          <t>Tập trung chuẩn xác vào Trang 18 (Field/Diary Study), chấm dứt việc nhại lại nguồn Trang 29.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="110" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Tầng 5 (Đối tượng)</t>
@@ -3469,55 +3485,53 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Chào Nam, việc xác định đối tượng (actor) là bước tiên quyết vì "AI chatbot" hay bất kỳ giải pháp nào cũng không phải là một bài toán cụ thể cho đến khi bạn xác định được đối tượng mục tiêu trang 8.
-Cụ thể, việc xác định đối tượng trước khi tìm bài toán là cần thiết vì ba lý do chính:
-Quyết định Workflow: Đối tượng khác nhau sẽ có quy trình làm việc và những công việc cần hỗ trợ khác nhau. Ví dụ, chatbot phục vụ khách hàng bên ngoài sẽ có workflow giải đáp FAQ/tư vấn mua hàng, trong khi chatbot hỗ trợ nội bộ lại có workflow phân loại ticket hoặc hỗ trợ nghiệp vụ cho nhân viên trang 8.
-Xác định Metric (chỉ số) đo lường: Đối tượng khác nhau dẫn đến mục tiêu thành công khác nhau. Với khách hàng, bạn có thể đo bằng tỷ lệ tự phục vụ (Self-service rate) hoặc mức độ hài lòng (CSAT). Với người dùng nội bộ, chỉ số quan trọng lại là thời gian xử lý công việc (Processing time) hoặc độ chính xác khi phân loại trang 8.
-Đánh giá rủi ro và nút thắt: Khi chưa xác định đối tượng cụ thể, bạn không thể biết ai đang bị quá tải, bước nào đang là nút thắt gây hao phí thời gian, hoặc ai là người chịu trách nhiệm phê duyệt khi AI gặp lỗi trang 8 trang 109.
-Nếu không có đối tượng, bạn sẽ chỉ đang xây dựng tính năng dựa trên công nghệ ("AI chatbot") thay vì giải quyết một bài toán thật sự có giá trị cho người dùng trang 8.</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>1285</v>
+          <t>Chào Nam, việc xác định đối tượng là bước tiên quyết... Quyết định Workflow trang 8... Xác định Metric trang 8... Đánh giá rủi ro trang 8 trang 109... Xây dựng tính năng trang 8.</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>trang 8 (lặp 4 lần), trang 109</t>
+        </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>• Xả 1.285 ký tự dài lê thê
-• Rò rỉ số trang ảo: 'trang 8 trang 109' (trong khi slide chỉ có ~33 trang)
-• Dẫn dắt 1 chiều, thiếu tính tương tác đa chiều</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
+          <t>k4-d2-slide-blue-Slide D301:
+• Tr. 8 (Đối tượng khác nhau dẫn đến workflow, metric, rủi ro khác nhau)</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>BỊA NGUỒN TRANG 109 (Phantom Citation):
+• Box nguồn ở dưới chỉ có DUY NHẤT 'Tr. 8'.
+• Trong text bot tự bịa thêm 'trang 109' hoàn toàn không có trong tài liệu nguồn bài giảng (Học viên click vào bị lỗi 404)!</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Xác định đối tượng là tiền đề bắt buộc vì: Đối tượng khác nhau sẽ quyết định Workflow khác nhau, Metric thành công khác nhau (CSAT vs Thời gian xử lý) và Nút thắt rủi ro khác nhau, tránh việc làm tính năng công nghệ mà không ai dùng.</t>
         </is>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="H10" s="9" t="n">
         <v>232</v>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="I10" s="41" t="inlineStr">
         <is>
           <t>Slide [k4-d2-slide-blue] · Trang 8</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="J10" s="10" t="inlineStr">
         <is>
           <t>• Option A: Làm sao để xác định nút thắt trong quy trình của đối tượng?
 • Option B: Các chỉ số (Metrics) đo lường thành công khác biệt thế nào giữa user nội bộ và khách hàng?</t>
         </is>
       </c>
-      <c r="J10" s="37" t="inlineStr">
-        <is>
-          <t>ĐÃ KHẮC PHỤC</t>
-        </is>
-      </c>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>Loại bỏ số trang ảo 109; cô đọng 3 trụ cột (Workflow, Metric, Risk) trong 2 câu; dẫn thẳng sang tìm nút thắt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="100" customHeight="1">
+          <t>Xóa bỏ triệt để nguồn bịa 'trang 109'; neo duy nhất và chuẩn xác vào Slide Trang 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="110" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Tầng 6 (Nút thắt)</t>
@@ -3530,68 +3544,52 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Để xác định nút thắt trong quy trình làm việc của đối tượng, bạn cần thực hiện quá trình phân tích sâu vào hành vi thực tế của họ thay vì chỉ nhìn vào bề nổi. Dưới đây là các phương pháp từ bài học để bạn thực hiện điều này trang 18:
-Quan sát trực tiếp và ghi chép hành vi:
-Sử dụng các kỹ thuật như quan sát thực tế (Field Study) hoặc nhật ký hành vi (Diary Study) để thấy rõ người dùng đang thực sự thao tác ra sao trang 18.
-Tìm kiếm các công đoạn mà họ đang phải thực hiện lặp đi lặp lại, những chỗ họ phải ngồi chờ, hoặc những tác vụ buộc phải copy-paste thủ công giữa các công cụ trang 19.
-Đặt câu hỏi chẩn đoán (4 câu hỏi): Khi nhận được đề bài, hãy hỏi ngược lại để tìm ra điểm nghẽn trang 12:
-Người dùng gặp khó khăn ở công đoạn nào?
-Ai đang quá tải và ở bước nào?
-Quy trình hiện tại đang xử lý các bước đó ra sao?
-Giải pháp này thực chất đang xây cho ai?
-Phân tách quy trình thành các bước nhỏ:
-Đừng nhìn quy trình như một khối tổng thể, hãy chia nhỏ nó ra theo từng mốc thời gian trang 24. Ví dụ, với một báo cáo tuần (Weekly Report), hãy liệt kê chi tiết: Export dữ liệu (15'), Lấy metrics (12'), Đọc Slack (10'), Viết narrative (25'), Review/Format (18'), Gửi (10') trang 24.
-Nút thắt chính là bước tốn nhiều thời gian nhất hoặc gây ra nhiều sai sót nhất (trong ví dụ trên là bước "Viết narrative" chiếm 25 phút) trang 24.
-Sử dụng kỹ thuật "5 Whys": Sau khi đã xác định được một vấn đề, hãy hỏi "Tại sao?" 5 lần để truy ngược lại nguồn gốc căn bản gây ra nút thắt đó, thay vì chỉ giải quyết triệu chứng bề ngoài trang 18.
-Khi đã xác định được bước nào gây tốn thời gian hay là điểm đau (pain point), bạn mới có cơ sở để định lượng và đề xuất giải pháp AI phù hợp tại chính bước đó trang 12 trang 24.
-Nguồn (4)
-k4-d2-slide-blue-Slide D301
-Tr. 18 * Quan sát thực tế
-Tr. 19 Lấy từ chính công việc...
-Tr. 12 01 Người dùng gặp...
-Tr. 24 Export Jira (15')...
-Hỏi tiếp
-Cách dùng ma trận Tác động – Nỗ lực để chọn bài toán?
-Làm sao để lượng hóa điểm đau của người dùng?</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>1820</v>
+          <t>Để xác định nút thắt... trang 18... trang 19... trang 12... trang 24... trang 18... trang 12 trang 24...</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>trang 18, trang 19, trang 12, trang 24 (rải rác khắp bài)</t>
+        </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>• Xả 'Bức tường chữ' cực đại: 1.820 ký tự (như một bài luận dài)
-• Độc thoại áp đặt, học viên không thể đọc hết giữa giờ học
-• Mục 'Hỏi tiếp' chỉ là 2 dòng text chết, không bấm được</t>
+          <t>k4-d2-slide-blue-Slide D301:
+• Tr. 18 (Field Study)
+• Tr. 19 (Việc lặp lại, ngồi chờ)
+• Tr. 12 (4 câu hỏi chẩn đoán)
+• Tr. 24 (Báo cáo tuần: viết narrative 25')</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
+          <t>BỨC TƯỜNG CHỮ CỰC ĐẠI &amp; KHÔNG BẤM ĐƯỢC:
+• Box nguồn ở dưới trích dẫn rất chuẩn 4 trang (12, 18, 19, 24).
+• Tuy nhiên trong text bot xả tới 1.820 ký tự và biến 2 câu hỏi gợi mở thành text chết, không hỗ trợ bấm nút tương tác.</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
           <t>Xác định nút thắt bằng 3 bước: (1) Chia nhỏ quy trình theo mốc thời gian (ví dụ báo cáo tuần: viết narrative chiếm 25' là nút thắt); (2) Đặt 4 câu hỏi chẩn đoán để tìm bước quá tải; và (3) Áp dụng kỹ thuật 5 Whys truy nguồn gốc rễ.</t>
         </is>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="H11" s="9" t="n">
         <v>235</v>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="I11" s="41" t="inlineStr">
         <is>
           <t>Slide [k4-d2-slide-blue] · Trang 12, Trang 18, Trang 24</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>• Option A (Nút tương tác): Cách dùng ma trận Tác động – Nỗ lực (Impact-Effort Matrix) để chọn bài toán?
-• Option B (Nút tương tác): Làm sao để lượng hóa điểm đau (Pain Point) của người dùng thành con số?</t>
-        </is>
-      </c>
-      <c r="J11" s="37" t="inlineStr">
-        <is>
-          <t>ĐÃ KHẮC PHỤC</t>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>• Option A: Cách dùng ma trận Tác động – Nỗ lực (Impact-Effort Matrix) để chọn bài toán?
+• Option B: Làm sao để lượng hóa điểm đau (Pain Point) của người dùng thành con số?</t>
         </is>
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>Giảm 87.1% độ dài (từ 1.820 ký tự xuống 235 ký tự); biến 2 câu text chết thành 2 nút bấm tương tác có viền neon ➔.</t>
+          <t>Thu gọn từ 1.820 xuống 235 ký tự; giữ nguyên trích dẫn 3 nguồn cốt lõi (12, 18, 24); biến 2 câu text chết thành nút bấm tương tác.</t>
         </is>
       </c>
     </row>
@@ -3599,8 +3597,8 @@
   <mergeCells count="4">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:K4"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A4:F4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
